--- a/Design/Excel/ET/Datas/Game/Skill.xlsx
+++ b/Design/Excel/ET/Datas/Game/Skill.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\XHFrameworkSkill\Luban\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4BEEDF-1BC3-416E-B41A-3C3AA6775AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74E7510-B390-4EED-8D41-9941B12DD9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -190,6 +190,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>

--- a/Design/Excel/ET/Datas/Game/Skill.xlsx
+++ b/Design/Excel/ET/Datas/Game/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74E7510-B390-4EED-8D41-9941B12DD9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB7E74A-C122-49A6-8CB5-F21C2B0F55F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4050" yWindow="3640" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -172,6 +172,14 @@
   </si>
   <si>
     <t>Sprites/SkillIcon/01109</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsAct</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -225,7 +233,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -233,6 +241,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -508,19 +517,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.9140625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="16.25" style="2" customWidth="1"/>
-    <col min="6" max="6" width="44.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.9140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="22.58203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="4.9140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="44.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="23" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.9140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="22.58203125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,24 +541,27 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>8</v>
+      <c r="D2" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -556,194 +569,234 @@
       <c r="F2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" t="s">
+      <c r="D4"/>
+      <c r="G4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>14</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>17</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>21</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
         <v>23</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>24</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
         <v>26</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>27</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>1007</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
         <v>29</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>30</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>1008</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
         <v>32</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>33</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>1009</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
         <v>35</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>1010</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>2001</v>
       </c>
       <c r="C15" t="s">
         <v>37</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
         <v>38</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>39</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>7001</v>
       </c>
       <c r="C16" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>42</v>
       </c>
     </row>

--- a/Design/Excel/ET/Datas/Game/Skill.xlsx
+++ b/Design/Excel/ET/Datas/Game/Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB7E74A-C122-49A6-8CB5-F21C2B0F55F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58DAF415-D844-4D74-A1B7-32E114E054A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4050" yWindow="3640" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Design/Excel/ET/Datas/Game/Skill.xlsx
+++ b/Design/Excel/ET/Datas/Game/Skill.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="H5" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5" s="0" t="n">
         <v>2</v>

--- a/Design/Excel/ET/Datas/Game/Skill.xlsx
+++ b/Design/Excel/ET/Datas/Game/Skill.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9689A58F-A166-44A1-A59A-03F4F280953F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E231273C-4171-4528-9433-546D19AF2C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4870" yWindow="790" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5210" yWindow="1130" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -67,9 +67,6 @@
     <t>##group</t>
   </si>
   <si>
-    <t>DesignerNote</t>
-  </si>
-  <si>
     <t>Icon</t>
   </si>
   <si>
@@ -79,9 +76,6 @@
     <t>TriggerType 0Active 1Passive</t>
   </si>
   <si>
-    <t>战士技能</t>
-  </si>
-  <si>
     <t>Sweep</t>
   </si>
   <si>
@@ -172,9 +166,6 @@
     <t>Sprites/SkillIcon/01110</t>
   </si>
   <si>
-    <t>战士被动</t>
-  </si>
-  <si>
     <t>BeRecBlood</t>
   </si>
   <si>
@@ -182,9 +173,6 @@
   </si>
   <si>
     <t>Sprites/SkillIcon/01210</t>
-  </si>
-  <si>
-    <t>小兵远程普攻</t>
   </si>
   <si>
     <t>FireCircle</t>
@@ -213,6 +201,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -523,60 +512,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="17.9140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="4.9140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="16.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="44.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="23" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.9140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="22.58203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="4.9140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.4140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.08203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="22.58203125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -585,325 +573,316 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
         <v>11</v>
       </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4"/>
+      <c r="F4" t="s">
         <v>15</v>
       </c>
-      <c r="D4"/>
       <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
         <v>16</v>
-      </c>
-      <c r="H4" t="s">
-        <v>7</v>
       </c>
       <c r="I4" t="s">
         <v>17</v>
       </c>
-      <c r="J4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>20</v>
       </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
+      <c r="G5">
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="D6">
-        <v>1</v>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
       </c>
       <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
+      <c r="G6">
+        <v>1</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
         <v>26</v>
       </c>
-      <c r="F7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" t="s">
-        <v>28</v>
+      <c r="G7">
+        <v>1</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
         <v>29</v>
       </c>
-      <c r="F8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" t="s">
-        <v>31</v>
+      <c r="G8">
+        <v>1</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="D9">
-        <v>1</v>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
       </c>
       <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
         <v>32</v>
       </c>
-      <c r="F9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" t="s">
-        <v>34</v>
+      <c r="G9">
+        <v>1</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="D10">
-        <v>1</v>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
       </c>
       <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" t="s">
         <v>35</v>
       </c>
-      <c r="F10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" t="s">
-        <v>37</v>
+      <c r="G10">
+        <v>1</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>1007</v>
       </c>
-      <c r="D11">
-        <v>1</v>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
       </c>
       <c r="E11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" t="s">
         <v>38</v>
       </c>
-      <c r="F11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" t="s">
-        <v>40</v>
+      <c r="G11">
+        <v>1</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>1008</v>
       </c>
-      <c r="D12">
-        <v>1</v>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>39</v>
       </c>
       <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
         <v>41</v>
       </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" t="s">
-        <v>43</v>
+      <c r="G12">
+        <v>1</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>1009</v>
       </c>
-      <c r="D13">
-        <v>1</v>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
       </c>
       <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>46</v>
+      <c r="G13">
+        <v>1</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>1010</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>49</v>
+      <c r="G14">
+        <v>1</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>2001</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" t="s">
         <v>50</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" t="s">
-        <v>53</v>
+      <c r="G15">
+        <v>1</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -911,33 +890,27 @@
       <c r="I15">
         <v>1</v>
       </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>7001</v>
       </c>
-      <c r="C16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" t="s">
-        <v>48</v>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
       </c>
       <c r="H16">
         <v>1</v>
       </c>
       <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16">
         <v>0</v>
       </c>
     </row>

--- a/Design/Excel/ET/Datas/Game/Skill.xlsx
+++ b/Design/Excel/ET/Datas/Game/Skill.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E231273C-4171-4528-9433-546D19AF2C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118DD35F-2CB7-4BCB-9049-B3E7CAA92D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5210" yWindow="1130" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2210" yWindow="2070" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
   <si>
     <t>##var</t>
   </si>
@@ -176,6 +176,14 @@
   </si>
   <si>
     <t>FireCircle</t>
+  </si>
+  <si>
+    <t>Quality</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -512,19 +520,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="4.9140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.25" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.4140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.08203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="22.58203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="4.9140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.4140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="22.58203125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -532,39 +540,42 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -573,344 +584,383 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="C4"/>
-      <c r="F4" t="s">
+      <c r="D4"/>
+      <c r="G4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>7</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
         <v>18</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>20</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>5</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
       <c r="I5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
         <v>21</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>22</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>23</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>25</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>26</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>28</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>29</v>
       </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
         <v>30</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>31</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>32</v>
       </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="I9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
         <v>33</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>34</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>35</v>
       </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
         <v>36</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>37</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>38</v>
       </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
         <v>39</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>40</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>41</v>
       </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
         <v>42</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="I14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>2001</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
         <v>48</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>49</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>50</v>
       </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>7001</v>
       </c>
       <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>46</v>
       </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
       <c r="H16">
         <v>1</v>
       </c>
       <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
         <v>0</v>
       </c>
     </row>

--- a/Design/Excel/ET/Datas/Game/Skill.xlsx
+++ b/Design/Excel/ET/Datas/Game/Skill.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118DD35F-2CB7-4BCB-9049-B3E7CAA92D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0A4E36-BE21-4B9E-A1F8-A8491B358580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2210" yWindow="2070" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -76,113 +76,125 @@
     <t>TriggerType 0Active 1Passive</t>
   </si>
   <si>
-    <t>Sweep</t>
-  </si>
-  <si>
     <t>横扫</t>
   </si>
   <si>
     <t>Sprites/SkillIcon/01101</t>
   </si>
   <si>
-    <t>Blood</t>
-  </si>
-  <si>
     <t>流血</t>
   </si>
   <si>
     <t>Sprites/SkillIcon/01102</t>
   </si>
   <si>
-    <t>RuFood</t>
-  </si>
-  <si>
     <t>践踏</t>
   </si>
   <si>
     <t>Sprites/SkillIcon/01103</t>
   </si>
   <si>
-    <t>Wind</t>
-  </si>
-  <si>
     <t>旋风斩</t>
   </si>
   <si>
     <t>Sprites/SkillIcon/01104</t>
   </si>
   <si>
-    <t>God</t>
-  </si>
-  <si>
     <t>神罗天正</t>
   </si>
   <si>
     <t>Sprites/SkillIcon/01105</t>
   </si>
   <si>
-    <t>Wan</t>
-  </si>
-  <si>
     <t>万象天引</t>
   </si>
   <si>
     <t>Sprites/SkillIcon/01106</t>
   </si>
   <si>
-    <t>RecBlood</t>
-  </si>
-  <si>
     <t>回血</t>
   </si>
   <si>
     <t>Sprites/SkillIcon/01107</t>
   </si>
   <si>
-    <t>ThreeFire</t>
-  </si>
-  <si>
     <t>三火球</t>
   </si>
   <si>
     <t>Sprites/SkillIcon/01108</t>
   </si>
   <si>
-    <t>SpeedUp</t>
-  </si>
-  <si>
     <t>急速</t>
   </si>
   <si>
     <t>Sprites/SkillIcon/01109</t>
   </si>
   <si>
-    <t>FireCircle2</t>
-  </si>
-  <si>
     <t>火球术</t>
   </si>
   <si>
     <t>Sprites/SkillIcon/01110</t>
   </si>
   <si>
-    <t>BeRecBlood</t>
-  </si>
-  <si>
     <t>被动回血</t>
   </si>
   <si>
     <t>Sprites/SkillIcon/01210</t>
   </si>
   <si>
-    <t>FireCircle</t>
-  </si>
-  <si>
     <t>Quality</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Sweep</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Blood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_RuFood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Wind</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_God</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Wan</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_RecBlood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_ThreeFire</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_SpeedUp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_FireCircle2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_BeRecBlood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_FireCircle</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -540,7 +552,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -572,7 +584,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>11</v>
@@ -629,14 +641,14 @@
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
         <v>18</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>19</v>
-      </c>
-      <c r="G5" t="s">
-        <v>20</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -658,14 +670,14 @@
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
         <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -688,13 +700,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -717,13 +729,13 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -745,14 +757,14 @@
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" t="s">
-        <v>30</v>
+      <c r="E9" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -774,14 +786,14 @@
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10" t="s">
-        <v>33</v>
+      <c r="E10" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -803,14 +815,14 @@
       <c r="D11">
         <v>1</v>
       </c>
-      <c r="E11" t="s">
-        <v>36</v>
+      <c r="E11" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -832,14 +844,14 @@
       <c r="D12">
         <v>1</v>
       </c>
-      <c r="E12" t="s">
-        <v>39</v>
+      <c r="E12" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -861,14 +873,14 @@
       <c r="D13">
         <v>1</v>
       </c>
-      <c r="E13" t="s">
-        <v>42</v>
+      <c r="E13" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -891,13 +903,13 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -919,14 +931,14 @@
       <c r="D15">
         <v>0</v>
       </c>
-      <c r="E15" t="s">
-        <v>48</v>
+      <c r="E15" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G15" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -949,10 +961,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H16">
         <v>1</v>

--- a/Design/Excel/ET/Datas/Game/Skill.xlsx
+++ b/Design/Excel/ET/Datas/Game/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0A4E36-BE21-4B9E-A1F8-A8491B358580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAB669A-675E-4D23-BCE9-D484571417FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5550" yWindow="2240" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
